--- a/实验记录表.xlsx
+++ b/实验记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kaggle\RSNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281F00BE-32B9-468A-8409-032FCF276A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E30EFEB-BE5A-46B6-A626-178304B60AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,6 +84,34 @@
   </si>
   <si>
     <t>在v1基础上，去掉label query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练所有序列里的slice，改为不重叠拼接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个 slot 的全部序列共享最多 32 个窗口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标签query提前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v1基础上，修改输入，按照公开代码的来，每个study选24个窗口，候选64个</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -419,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.58203125" customWidth="1"/>
@@ -515,6 +543,68 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="C6" s="1">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.87797000000000003</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.90600000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.91200000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.89587000000000006</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/实验记录表.xlsx
+++ b/实验记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kaggle\RSNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E30EFEB-BE5A-46B6-A626-178304B60AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C62BA3E-B6B2-4716-AD09-48D69C04700B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,7 +111,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>v1基础上，修改输入，按照公开代码的来，每个study选24个窗口，候选64个</t>
+    <t>v9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v1基础上，修改输入，按照公开代码的来，每个study选24个窗口，候选64个，同时将label query提前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v8基础上，将候选slice提高到80，23/17/15/10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在v9基础上关闭metadata</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在v9基础上加上ema 0.9995</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v10 swa 平均融合最好和次好的两个权重,0.9077和0.9074</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -447,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.58203125" customWidth="1"/>
@@ -597,13 +625,84 @@
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>12</v>
       </c>
       <c r="D10" s="1">
         <v>0.89587000000000006</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.89688000000000001</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.89785999999999999</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.92500000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.90547999999999995</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.90769999999999995</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.92700000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/实验记录表.xlsx
+++ b/实验记录表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kaggle\RSNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C62BA3E-B6B2-4716-AD09-48D69C04700B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19436B9F-0616-43F0-85C5-EDE78CD785A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -140,6 +140,46 @@
   </si>
   <si>
     <t>v10 swa 平均融合最好和次好的两个权重,0.9077和0.9074</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在v10基础上，将dino的输出改为cls和path的均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>训练固定 24 窗口，五 slot 配额 7/5/5/3/4，沿物理深度分层随机抽样。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v10基础上，提高选取slot的质量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>label2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>label3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置编码改为rope</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -475,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.58203125" customWidth="1"/>
@@ -705,6 +745,96 @@
         <v>0.92700000000000005</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.90541000000000005</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.89480999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.91100000000000003</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.91022000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.91202000000000005</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="1">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.90530999999999995</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/实验记录表.xlsx
+++ b/实验记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kaggle\RSNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19436B9F-0616-43F0-85C5-EDE78CD785A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C52480B-5337-4B9A-B5C6-6E9AE18274B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,6 +180,30 @@
   </si>
   <si>
     <t>位置编码改为rope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新划分验证集，不再用58张验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接在原图上数据增强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v17_v1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原图+ 增强的一起训练</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -515,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.58203125" customWidth="1"/>
@@ -835,6 +859,54 @@
         <v>0.92800000000000005</v>
       </c>
     </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="1">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.90725</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.92300000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.91042999999999996</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.90790000000000004</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/实验记录表.xlsx
+++ b/实验记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kaggle\RSNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C52480B-5337-4B9A-B5C6-6E9AE18274B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E237752-F197-4255-92A8-BDABAC44E71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +204,45 @@
   </si>
   <si>
     <t>原图+ 增强的一起训练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三通道改成按物理距离选邻居</t>
+  </si>
+  <si>
+    <t>v19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最多两个序列，候选120 ， 窗口36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五折训练，验证集用分出来的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>backbone radimagenet resnte50 backbone lr 3e-4 imgsz224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mq model</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,11 +578,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.58203125" customWidth="1"/>
-    <col min="2" max="2" width="69.4140625" customWidth="1"/>
+    <col min="2" max="2" width="85.25" customWidth="1"/>
     <col min="3" max="3" width="24.9140625" customWidth="1"/>
     <col min="4" max="4" width="22.08203125" customWidth="1"/>
   </cols>
@@ -906,6 +945,88 @@
       <c r="D23" s="1">
         <v>0.90790000000000004</v>
       </c>
+      <c r="E23" s="1">
+        <v>0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.91173000000000004</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.92600000000000005</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.90400000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.90475000000000005</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.92600000000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="1">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.90720000000000001</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.92800000000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="1">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.91069999999999995</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.92500000000000004</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/实验记录表.xlsx
+++ b/实验记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kaggle\RSNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E237752-F197-4255-92A8-BDABAC44E71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8457301B-F643-44F2-B310-7395EBFE2A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>版本</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -243,6 +243,14 @@
   </si>
   <si>
     <t>mq model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resnet 五折</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.58203125" customWidth="1"/>
@@ -1028,6 +1036,18 @@
         <v>0.92500000000000004</v>
       </c>
     </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1">
+        <v>0.92900000000000005</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
